--- a/data/xlsx/dte--4g-6g-welding.xlsx
+++ b/data/xlsx/dte--4g-6g-welding.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -1075,9 +1075,17 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="14.15" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the institute should have at least 8 welding booths. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A1:G1"/>
